--- a/data/SPO_GRADE_Certainty.xlsx
+++ b/data/SPO_GRADE_Certainty.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoregon-my.sharepoint.com/personal/strevino_uoregon_edu/Documents/Desktop/HEDCO Institute/GitHub R Projects/Suicide_Prevention_Overview_Dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B25FF822-BCDD-43BC-B6B0-99E7BE278187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{88B69727-5F78-46BA-A7C2-EEA081037C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21669C56-472B-4D6E-B0EC-0756C2D852EC}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EB0631BE-0FA5-4BD1-869E-3FDBE0412C6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB0631BE-0FA5-4BD1-869E-3FDBE0412C6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$27</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,6 +48,7 @@
     <author>tc={28353D2E-7AE0-4F76-880F-EABB788C089A}</author>
     <author>tc={66E9B180-C5C1-449B-808B-44766F60329F}</author>
     <author>tc={8934C9EC-E1EE-46D6-8DA8-2B9FF162A1D0}</author>
+    <author>tc={BED55A21-DC3F-4007-9678-FB4C496D0766}</author>
     <author>tc={F97111A4-3E40-475D-BCDC-D4AE2090472B}</author>
     <author>tc={37468D20-E42D-4E43-A7AE-E2A7524B0D3F}</author>
     <author>tc={0EEE13B2-EA02-4E2A-815B-BC8F36563422}</author>
@@ -58,6 +62,7 @@
     <author>tc={2F778D81-DE7A-4394-899F-038ACDD67517}</author>
     <author>tc={272C082C-5B13-4083-8E83-30FFD115F080}</author>
     <author>tc={6A8CDA2D-B191-45D2-8FA0-3B85CBC64D5A}</author>
+    <author>tc={86961469-68F5-4DE4-B96E-A21549C91143}</author>
     <author>tc={B3B7AC91-FBC3-436C-82DE-F9246BC66C0F}</author>
     <author>tc={2798BFEA-60F3-4E8B-9832-0E195CC4609F}</author>
     <author>tc={70137FD6-38FC-4956-8CCE-9C05872757C7}</author>
@@ -100,12 +105,14 @@
     <author>tc={F5F68A18-B196-496A-8321-70E2B7462312}</author>
     <author>tc={4FA52890-0546-4EF8-B6F5-9F2BAB9EAF7A}</author>
     <author>tc={5DD21839-2B0C-418E-B342-E81FEC740430}</author>
+    <author>tc={25CA98DB-9416-4171-B283-93B8471A8D4C}</author>
     <author>tc={B375F206-DA05-4342-8601-843499F31D95}</author>
     <author>tc={7C918D85-D143-4E29-A4B7-893AFAB162C7}</author>
     <author>tc={64809464-A8FF-4AA3-9E15-C4B61D224BBB}</author>
     <author>tc={68E69489-9217-45A0-B653-7D84F8FCAEF4}</author>
     <author>tc={9B79FE53-847C-4C16-903B-FA0D5756F932}</author>
     <author>tc={99297B65-3A3E-4912-A925-C2EE27D33BA1}</author>
+    <author>tc={8C0BDE33-B1B8-4444-945F-536D8A6CE891}</author>
     <author>tc={7D1AEF54-A107-4CB5-82AC-2827C98B97E0}</author>
     <author>tc={B9813C9C-17B2-49D9-80A5-95CB63111600}</author>
     <author>tc={BD1E6973-16D9-469B-8084-933FD5032366}</author>
@@ -154,7 +161,15 @@
     Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</t>
       </text>
     </comment>
-    <comment ref="I3" authorId="4" shapeId="0" xr:uid="{F97111A4-3E40-475D-BCDC-D4AE2090472B}">
+    <comment ref="P2" authorId="4" shapeId="0" xr:uid="{BED55A21-DC3F-4007-9678-FB4C496D0766}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed from “may not” to “may” due to OR = 1.19</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="5" shapeId="0" xr:uid="{F97111A4-3E40-475D-BCDC-D4AE2090472B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +177,7 @@
     Odds ratios are transformed from log odds. Note this estimate is identical to the one below and may reflect an error.</t>
       </text>
     </comment>
-    <comment ref="J3" authorId="5" shapeId="0" xr:uid="{37468D20-E42D-4E43-A7AE-E2A7524B0D3F}">
+    <comment ref="J3" authorId="6" shapeId="0" xr:uid="{37468D20-E42D-4E43-A7AE-E2A7524B0D3F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -170,7 +185,7 @@
     Downgraded two levels due to very serious risk of bias; 80.5% of RCTs and all non-randomized studies were rated high risk of bias, and higher-risk studies showed larger effects in meta-regression analyses.</t>
       </text>
     </comment>
-    <comment ref="K3" authorId="6" shapeId="0" xr:uid="{0EEE13B2-EA02-4E2A-815B-BC8F36563422}">
+    <comment ref="K3" authorId="7" shapeId="0" xr:uid="{0EEE13B2-EA02-4E2A-815B-BC8F36563422}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -178,7 +193,7 @@
     inconsistency could not be fully evaluated because estimate-specific heterogeneity information was unavailable</t>
       </text>
     </comment>
-    <comment ref="M3" authorId="7" shapeId="0" xr:uid="{C89531CB-6DC8-40FB-8017-184ECFBD8FD2}">
+    <comment ref="M3" authorId="8" shapeId="0" xr:uid="{C89531CB-6DC8-40FB-8017-184ECFBD8FD2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -186,7 +201,7 @@
     Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</t>
       </text>
     </comment>
-    <comment ref="I4" authorId="8" shapeId="0" xr:uid="{BB30A2BF-ECB9-4B49-8532-8B94325B1467}">
+    <comment ref="I4" authorId="9" shapeId="0" xr:uid="{BB30A2BF-ECB9-4B49-8532-8B94325B1467}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -194,7 +209,7 @@
     Odds ratios are transformed from log odds. Note this estimate is identical to the one above and may reflect an error.</t>
       </text>
     </comment>
-    <comment ref="J4" authorId="9" shapeId="0" xr:uid="{D97AC3B5-80B2-4BE1-9DB6-F50FCE3B5218}">
+    <comment ref="J4" authorId="10" shapeId="0" xr:uid="{D97AC3B5-80B2-4BE1-9DB6-F50FCE3B5218}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -202,7 +217,7 @@
     Downgraded two levels due to very serious risk of bias; 80.5% of RCTs and all non-randomized studies were rated high risk of bias, and higher-risk studies showed larger effects in meta-regression analyses.</t>
       </text>
     </comment>
-    <comment ref="K4" authorId="10" shapeId="0" xr:uid="{A7B08377-BF2C-4CDF-A979-1085936645C6}">
+    <comment ref="K4" authorId="11" shapeId="0" xr:uid="{A7B08377-BF2C-4CDF-A979-1085936645C6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -210,7 +225,7 @@
     inconsistency could not be fully evaluated because estimate-specific heterogeneity information was unavailable</t>
       </text>
     </comment>
-    <comment ref="M4" authorId="11" shapeId="0" xr:uid="{C34ED7EE-310D-49C2-A1DD-5FBC4486DA13}">
+    <comment ref="M4" authorId="12" shapeId="0" xr:uid="{C34ED7EE-310D-49C2-A1DD-5FBC4486DA13}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -218,7 +233,7 @@
     Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</t>
       </text>
     </comment>
-    <comment ref="J5" authorId="12" shapeId="0" xr:uid="{53F03742-997A-445E-A39B-5C12442C2F83}">
+    <comment ref="J5" authorId="13" shapeId="0" xr:uid="{53F03742-997A-445E-A39B-5C12442C2F83}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -226,7 +241,7 @@
     Downgraded two levels due to very serious risk of bias; 80.5% of RCTs and all non-randomized studies were rated high risk of bias, and higher-risk studies showed larger effects in meta-regression analyses.</t>
       </text>
     </comment>
-    <comment ref="K5" authorId="13" shapeId="0" xr:uid="{AE0D97B2-3774-4198-86E5-80BA0FCBDED5}">
+    <comment ref="K5" authorId="14" shapeId="0" xr:uid="{AE0D97B2-3774-4198-86E5-80BA0FCBDED5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -234,7 +249,7 @@
     inconsistency could not be fully evaluated because estimate-specific heterogeneity information was unavailable</t>
       </text>
     </comment>
-    <comment ref="J6" authorId="14" shapeId="0" xr:uid="{2F778D81-DE7A-4394-899F-038ACDD67517}">
+    <comment ref="J6" authorId="15" shapeId="0" xr:uid="{2F778D81-DE7A-4394-899F-038ACDD67517}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -242,7 +257,7 @@
     Downgraded two levels due to very serious risk of bias; 80.5% of RCTs and all non-randomized studies were rated high risk of bias, and higher-risk studies showed larger effects in meta-regression analyses.</t>
       </text>
     </comment>
-    <comment ref="K6" authorId="15" shapeId="0" xr:uid="{272C082C-5B13-4083-8E83-30FFD115F080}">
+    <comment ref="K6" authorId="16" shapeId="0" xr:uid="{272C082C-5B13-4083-8E83-30FFD115F080}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -250,7 +265,7 @@
     inconsistency could not be fully evaluated because estimate-specific heterogeneity information was unavailable</t>
       </text>
     </comment>
-    <comment ref="M6" authorId="16" shapeId="0" xr:uid="{6A8CDA2D-B191-45D2-8FA0-3B85CBC64D5A}">
+    <comment ref="M6" authorId="17" shapeId="0" xr:uid="{6A8CDA2D-B191-45D2-8FA0-3B85CBC64D5A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -258,7 +273,15 @@
     Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</t>
       </text>
     </comment>
-    <comment ref="J7" authorId="17" shapeId="0" xr:uid="{B3B7AC91-FBC3-436C-82DE-F9246BC66C0F}">
+    <comment ref="P6" authorId="18" shapeId="0" xr:uid="{86961469-68F5-4DE4-B96E-A21549C91143}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed from “may not” to “may” due to SMD = -0.07, which is just outside -0.05 threshold.</t>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="19" shapeId="0" xr:uid="{B3B7AC91-FBC3-436C-82DE-F9246BC66C0F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -266,7 +289,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K7" authorId="18" shapeId="0" xr:uid="{2798BFEA-60F3-4E8B-9832-0E195CC4609F}">
+    <comment ref="K7" authorId="20" shapeId="0" xr:uid="{2798BFEA-60F3-4E8B-9832-0E195CC4609F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -274,7 +297,7 @@
     Heterogeneity is high, but 8/9 effect sizes in the meta-analysis are positive, and the negative one is ns, so not too concerning for the purposes of influencing recommendations.</t>
       </text>
     </comment>
-    <comment ref="N7" authorId="19" shapeId="0" xr:uid="{70137FD6-38FC-4956-8CCE-9C05872757C7}">
+    <comment ref="N7" authorId="21" shapeId="0" xr:uid="{70137FD6-38FC-4956-8CCE-9C05872757C7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -282,7 +305,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="J8" authorId="20" shapeId="0" xr:uid="{47FEAAFC-857F-4EFD-91C9-DC228EAF25EF}">
+    <comment ref="J8" authorId="22" shapeId="0" xr:uid="{47FEAAFC-857F-4EFD-91C9-DC228EAF25EF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -290,7 +313,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="21" shapeId="0" xr:uid="{D193324C-DA70-4D65-990A-73B981399FD1}">
+    <comment ref="K8" authorId="23" shapeId="0" xr:uid="{D193324C-DA70-4D65-990A-73B981399FD1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -298,7 +321,7 @@
     Heterogeneity is high, but all effect sizes in the meta-analysis are positive, although one is ns., but not too concerning for an overall recommendation about benefit vs. harm.</t>
       </text>
     </comment>
-    <comment ref="N8" authorId="22" shapeId="0" xr:uid="{5FEB427D-344C-486E-90EB-0156A4EA58C6}">
+    <comment ref="N8" authorId="24" shapeId="0" xr:uid="{5FEB427D-344C-486E-90EB-0156A4EA58C6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -306,7 +329,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="I9" authorId="23" shapeId="0" xr:uid="{45BE59DF-21E1-4E02-9210-AD203AEA6AEF}">
+    <comment ref="I9" authorId="25" shapeId="0" xr:uid="{45BE59DF-21E1-4E02-9210-AD203AEA6AEF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -314,7 +337,7 @@
     Note: The upper limit of the confidence interval was corrected by our team from -0.07 to 0.07, based on the corresponding p-value</t>
       </text>
     </comment>
-    <comment ref="J9" authorId="24" shapeId="0" xr:uid="{F5B1507A-C007-4669-B021-9E516FA82B17}">
+    <comment ref="J9" authorId="26" shapeId="0" xr:uid="{F5B1507A-C007-4669-B021-9E516FA82B17}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -322,7 +345,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="25" shapeId="0" xr:uid="{50D93BF0-FBBA-4D46-AC92-A46AA338581F}">
+    <comment ref="K9" authorId="27" shapeId="0" xr:uid="{50D93BF0-FBBA-4D46-AC92-A46AA338581F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -330,7 +353,7 @@
     Heterogeneity is high in the forest plot of Suicidal Ideation at post-test overall, but 8/9 effect sizes in the meta-analysis are positive, and the negative one is ns, so not too concerning for the purposes of influencing recommendations. Not reported separately for each subgroup.</t>
       </text>
     </comment>
-    <comment ref="M9" authorId="26" shapeId="0" xr:uid="{163ABB7A-5B7B-4A4E-A4FD-D08275FE6EE5}">
+    <comment ref="M9" authorId="28" shapeId="0" xr:uid="{163ABB7A-5B7B-4A4E-A4FD-D08275FE6EE5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -338,7 +361,7 @@
     Note that this assessment is based on an updated confidence interval of (-.05 to .07). The author-reported confidence interval was -.07, but we updated it to align with the reported p-value</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="27" shapeId="0" xr:uid="{E3DABF5B-0173-45BC-BE0D-8E0DFA1E16E7}">
+    <comment ref="N9" authorId="29" shapeId="0" xr:uid="{E3DABF5B-0173-45BC-BE0D-8E0DFA1E16E7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -346,7 +369,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="J10" authorId="28" shapeId="0" xr:uid="{879BE13B-D762-4060-8478-E7D02519DEA4}">
+    <comment ref="J10" authorId="30" shapeId="0" xr:uid="{879BE13B-D762-4060-8478-E7D02519DEA4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -354,7 +377,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="29" shapeId="0" xr:uid="{27B6B1E7-F055-4A3E-8878-8F58B513A361}">
+    <comment ref="K10" authorId="31" shapeId="0" xr:uid="{27B6B1E7-F055-4A3E-8878-8F58B513A361}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -362,7 +385,7 @@
     Heterogeneity is high in the forest plot but 6/7 effect sizes are positive and the negative one is ns.</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="30" shapeId="0" xr:uid="{D85EFC49-4D8A-45E7-A263-D13CD3CFBB31}">
+    <comment ref="N10" authorId="32" shapeId="0" xr:uid="{D85EFC49-4D8A-45E7-A263-D13CD3CFBB31}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -370,7 +393,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="I11" authorId="31" shapeId="0" xr:uid="{161BD65A-AD95-4C2D-8F8F-B5D340D33F10}">
+    <comment ref="I11" authorId="33" shapeId="0" xr:uid="{161BD65A-AD95-4C2D-8F8F-B5D340D33F10}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -379,7 +402,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="J11" authorId="32" shapeId="0" xr:uid="{A6BB221F-A677-437A-8E18-81E04C802B91}">
+    <comment ref="J11" authorId="34" shapeId="0" xr:uid="{A6BB221F-A677-437A-8E18-81E04C802B91}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -387,7 +410,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="33" shapeId="0" xr:uid="{277FC139-A7A2-473A-991D-D7B59A79BB70}">
+    <comment ref="K11" authorId="35" shapeId="0" xr:uid="{277FC139-A7A2-473A-991D-D7B59A79BB70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -395,7 +418,7 @@
     Heterogeneity all effect sizes in the forest plot are positive</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="34" shapeId="0" xr:uid="{BB85B066-8EF9-41C4-92D7-15A3D5111CBA}">
+    <comment ref="N11" authorId="36" shapeId="0" xr:uid="{BB85B066-8EF9-41C4-92D7-15A3D5111CBA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -403,7 +426,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="35" shapeId="0" xr:uid="{200595A8-F6FE-4A40-9274-15AADE4374A1}">
+    <comment ref="J12" authorId="37" shapeId="0" xr:uid="{200595A8-F6FE-4A40-9274-15AADE4374A1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -411,7 +434,7 @@
     Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="36" shapeId="0" xr:uid="{35D0F337-8030-4E5C-8AC2-1694E2E14218}">
+    <comment ref="K12" authorId="38" shapeId="0" xr:uid="{35D0F337-8030-4E5C-8AC2-1694E2E14218}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -419,7 +442,7 @@
     Heterogeneity is high in the forest plot but 6/7 effect sizes are positive and the negative one is ns.</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="37" shapeId="0" xr:uid="{BA5714D2-CEC4-428D-9D3E-BFB916BF0631}">
+    <comment ref="N12" authorId="39" shapeId="0" xr:uid="{BA5714D2-CEC4-428D-9D3E-BFB916BF0631}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -427,7 +450,7 @@
     Although funnel plot asymmetry suggested possible small-study effects and study eligibility was based on reporting suicide-related outcomes, trim-and-fill analyses did not identify missing studies or materially affect the pooled estimate.</t>
       </text>
     </comment>
-    <comment ref="J13" authorId="38" shapeId="0" xr:uid="{15D16867-5B9C-4157-AA3F-B86CE28FD8B9}">
+    <comment ref="J13" authorId="40" shapeId="0" xr:uid="{15D16867-5B9C-4157-AA3F-B86CE28FD8B9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -435,7 +458,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="39" shapeId="0" xr:uid="{2689D2EE-3B58-40CD-A483-5EB5AF49969F}">
+    <comment ref="N13" authorId="41" shapeId="0" xr:uid="{2689D2EE-3B58-40CD-A483-5EB5AF49969F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -443,7 +466,7 @@
     There was no evidence of small-study effects or publication bias based on Egger's regression test, and sampling variance was not significantly associated with effect size for either crude or adjusted suicidal ideation estimates.</t>
       </text>
     </comment>
-    <comment ref="J14" authorId="40" shapeId="0" xr:uid="{5CE2FA4B-24F1-4BA4-A071-0A539DEEE4CD}">
+    <comment ref="J14" authorId="42" shapeId="0" xr:uid="{5CE2FA4B-24F1-4BA4-A071-0A539DEEE4CD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -451,7 +474,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="N14" authorId="41" shapeId="0" xr:uid="{169B32BF-6551-4C39-B79D-2D17AE8AB70A}">
+    <comment ref="N14" authorId="43" shapeId="0" xr:uid="{169B32BF-6551-4C39-B79D-2D17AE8AB70A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -459,7 +482,7 @@
     There was no evidence of small-study effects or publication bias based on Egger's regression test, and sampling variance was not significantly associated with effect size for either crude or adjusted suicide attempt estimates.</t>
       </text>
     </comment>
-    <comment ref="I15" authorId="42" shapeId="0" xr:uid="{509E9E4B-C231-4DDE-A7D6-71646BA2CA91}">
+    <comment ref="I15" authorId="44" shapeId="0" xr:uid="{509E9E4B-C231-4DDE-A7D6-71646BA2CA91}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -467,7 +490,7 @@
     We transformed the author-reported log odds ratio for the contrast to get the contrast OR</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="43" shapeId="0" xr:uid="{9547B571-E64D-4EED-A9C9-60146171F3AE}">
+    <comment ref="J15" authorId="45" shapeId="0" xr:uid="{9547B571-E64D-4EED-A9C9-60146171F3AE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -475,7 +498,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="44" shapeId="0" xr:uid="{5D487D51-BA0D-46E9-966A-7C28F55260EA}">
+    <comment ref="K15" authorId="46" shapeId="0" xr:uid="{5D487D51-BA0D-46E9-966A-7C28F55260EA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -483,7 +506,7 @@
     No important residual heterogeneity was observed following moderator analysis (I²within = 0%; I²between = 0%).</t>
       </text>
     </comment>
-    <comment ref="M15" authorId="45" shapeId="0" xr:uid="{3D4BBEBC-0637-4E18-AEE3-403C19308198}">
+    <comment ref="M15" authorId="47" shapeId="0" xr:uid="{3D4BBEBC-0637-4E18-AEE3-403C19308198}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -491,7 +514,7 @@
     The confidence interval for the subgroup difference (OR 1.57, 95% CI 0.93 to 2.61) included both a potentially important difference between interventions involving teachers/counsellors and those without school stakeholder involvement and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="I16" authorId="46" shapeId="0" xr:uid="{DBBCFA00-869B-4BBC-9543-8744B9EA0E37}">
+    <comment ref="I16" authorId="48" shapeId="0" xr:uid="{DBBCFA00-869B-4BBC-9543-8744B9EA0E37}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -499,7 +522,7 @@
     We transformed the author-reported log odds ratio for the contrast to get the contrast OR</t>
       </text>
     </comment>
-    <comment ref="J16" authorId="47" shapeId="0" xr:uid="{90E50DE7-7A7E-41EF-8412-B3C7F2357837}">
+    <comment ref="J16" authorId="49" shapeId="0" xr:uid="{90E50DE7-7A7E-41EF-8412-B3C7F2357837}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -507,7 +530,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="48" shapeId="0" xr:uid="{15968271-164F-41E3-85C5-5A1F15B72FB3}">
+    <comment ref="K16" authorId="50" shapeId="0" xr:uid="{15968271-164F-41E3-85C5-5A1F15B72FB3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -515,7 +538,7 @@
     No important residual heterogeneity was observed following moderator analysis (I²within = 0%; I²between = 0%).</t>
       </text>
     </comment>
-    <comment ref="M16" authorId="49" shapeId="0" xr:uid="{6E20D627-403F-4685-97D2-A6713328E585}">
+    <comment ref="M16" authorId="51" shapeId="0" xr:uid="{6E20D627-403F-4685-97D2-A6713328E585}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -523,7 +546,7 @@
     The confidence interval for the subgroup difference (OR 0.92, 95% CI 0.59 to 1.45) included both potentially important differences between interventions with and without multi-stakeholder involvement and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="I17" authorId="50" shapeId="0" xr:uid="{4091987B-BADF-4DA0-A299-5F49E856AAFE}">
+    <comment ref="I17" authorId="52" shapeId="0" xr:uid="{4091987B-BADF-4DA0-A299-5F49E856AAFE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -531,7 +554,7 @@
     We transformed the author-reported log odds ratio for the contrast to get the contrast OR</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="51" shapeId="0" xr:uid="{8D6BD049-FB4E-43AD-9362-18F8A43403E8}">
+    <comment ref="J17" authorId="53" shapeId="0" xr:uid="{8D6BD049-FB4E-43AD-9362-18F8A43403E8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -539,7 +562,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="52" shapeId="0" xr:uid="{60423266-5210-4D8C-96CA-4219C20D29A3}">
+    <comment ref="K17" authorId="54" shapeId="0" xr:uid="{60423266-5210-4D8C-96CA-4219C20D29A3}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -547,7 +570,7 @@
     No important residual heterogeneity was observed following moderator analysis </t>
       </text>
     </comment>
-    <comment ref="M17" authorId="53" shapeId="0" xr:uid="{ACABE47E-2CEE-42DF-991D-7947CDE7F741}">
+    <comment ref="M17" authorId="55" shapeId="0" xr:uid="{ACABE47E-2CEE-42DF-991D-7947CDE7F741}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -555,7 +578,7 @@
     The confidence interval for the subgroup difference was wide (OR 0.60, 95% CI 0.35 to 1.02) and included both a potentially important difference between interventions targeting STBs and those not targeting STBs and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="54" shapeId="0" xr:uid="{CE1E1E0B-E34A-4A37-BE35-0972734C69AE}">
+    <comment ref="N17" authorId="56" shapeId="0" xr:uid="{CE1E1E0B-E34A-4A37-BE35-0972734C69AE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -563,7 +586,7 @@
     There was no evidence of small-study effects or publication bias based on Egger's regression test, and sampling variance was not significantly associated with effect size for either crude or adjusted suicide attempt estimates.</t>
       </text>
     </comment>
-    <comment ref="I18" authorId="55" shapeId="0" xr:uid="{4CDA3B0C-93C5-4E70-A860-F8093991D033}">
+    <comment ref="I18" authorId="57" shapeId="0" xr:uid="{4CDA3B0C-93C5-4E70-A860-F8093991D033}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -571,7 +594,7 @@
     We transformed the author-reported log odds ratio for the contrast to get the contrast OR</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="56" shapeId="0" xr:uid="{F5F68A18-B196-496A-8321-70E2B7462312}">
+    <comment ref="J18" authorId="58" shapeId="0" xr:uid="{F5F68A18-B196-496A-8321-70E2B7462312}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -579,7 +602,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="57" shapeId="0" xr:uid="{4FA52890-0546-4EF8-B6F5-9F2BAB9EAF7A}">
+    <comment ref="K18" authorId="59" shapeId="0" xr:uid="{4FA52890-0546-4EF8-B6F5-9F2BAB9EAF7A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -587,7 +610,7 @@
     Little residual heterogeneity remained following moderator analysis (I²between = 1.68%; I²within = 0%).</t>
       </text>
     </comment>
-    <comment ref="M18" authorId="58" shapeId="0" xr:uid="{5DD21839-2B0C-418E-B342-E81FEC740430}">
+    <comment ref="M18" authorId="60" shapeId="0" xr:uid="{5DD21839-2B0C-418E-B342-E81FEC740430}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -595,7 +618,15 @@
     The confidence interval for the subgroup difference (OR 0.85, 95% CI 0.55 to 1.30) included both potentially important differences between follow-up periods and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="J19" authorId="59" shapeId="0" xr:uid="{B375F206-DA05-4342-8601-843499F31D95}">
+    <comment ref="P18" authorId="61" shapeId="0" xr:uid="{25CA98DB-9416-4171-B283-93B8471A8D4C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed from “may not” to “may” due to contrast OR = 0.85, which is below lower threshold bound of 0.91. Also added effect direction of more for 12-months due to OR &lt;1 relative to reference group.</t>
+      </text>
+    </comment>
+    <comment ref="J19" authorId="62" shapeId="0" xr:uid="{B375F206-DA05-4342-8601-843499F31D95}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -603,7 +634,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="60" shapeId="0" xr:uid="{7C918D85-D143-4E29-A4B7-893AFAB162C7}">
+    <comment ref="K19" authorId="63" shapeId="0" xr:uid="{7C918D85-D143-4E29-A4B7-893AFAB162C7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -611,7 +642,7 @@
     Little residual heterogeneity remained following moderator analysis (I²between = 1.68%; I²within = 0%).</t>
       </text>
     </comment>
-    <comment ref="M19" authorId="61" shapeId="0" xr:uid="{64809464-A8FF-4AA3-9E15-C4B61D224BBB}">
+    <comment ref="M19" authorId="64" shapeId="0" xr:uid="{64809464-A8FF-4AA3-9E15-C4B61D224BBB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -619,7 +650,7 @@
     The confidence interval for the subgroup difference (OR 1.52, 95% CI 0.90 to 2.59) included both a potentially important difference between follow-up periods and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="J20" authorId="62" shapeId="0" xr:uid="{68E69489-9217-45A0-B653-7D84F8FCAEF4}">
+    <comment ref="J20" authorId="65" shapeId="0" xr:uid="{68E69489-9217-45A0-B653-7D84F8FCAEF4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -627,7 +658,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="63" shapeId="0" xr:uid="{9B79FE53-847C-4C16-903B-FA0D5756F932}">
+    <comment ref="K20" authorId="66" shapeId="0" xr:uid="{9B79FE53-847C-4C16-903B-FA0D5756F932}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -635,7 +666,7 @@
     No important residual heterogeneity was observed following moderator analysis (I²between = 0%; I²within = 0%).</t>
       </text>
     </comment>
-    <comment ref="M20" authorId="64" shapeId="0" xr:uid="{99297B65-3A3E-4912-A925-C2EE27D33BA1}">
+    <comment ref="M20" authorId="67" shapeId="0" xr:uid="{99297B65-3A3E-4912-A925-C2EE27D33BA1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -643,7 +674,15 @@
     The confidence interval for the subgroup difference (OR 1.13, 95% CI 0.76 to 1.68) included both potentially important differences between intervention durations and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="J21" authorId="65" shapeId="0" xr:uid="{7D1AEF54-A107-4CB5-82AC-2827C98B97E0}">
+    <comment ref="P20" authorId="68" shapeId="0" xr:uid="{8C0BDE33-B1B8-4444-945F-536D8A6CE891}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed from “may not” to “may” due to contrast OR 1.13, which is above upper threshold of 1.10. Also added direction of difference.</t>
+      </text>
+    </comment>
+    <comment ref="J21" authorId="69" shapeId="0" xr:uid="{7D1AEF54-A107-4CB5-82AC-2827C98B97E0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -651,7 +690,7 @@
     Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="66" shapeId="0" xr:uid="{B9813C9C-17B2-49D9-80A5-95CB63111600}">
+    <comment ref="K21" authorId="70" shapeId="0" xr:uid="{B9813C9C-17B2-49D9-80A5-95CB63111600}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -659,7 +698,7 @@
     No important residual heterogeneity was observed following moderator analysis (I²between = 0%; I²within = 0%).</t>
       </text>
     </comment>
-    <comment ref="M21" authorId="67" shapeId="0" xr:uid="{BD1E6973-16D9-469B-8084-933FD5032366}">
+    <comment ref="M21" authorId="71" shapeId="0" xr:uid="{BD1E6973-16D9-469B-8084-933FD5032366}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -667,7 +706,7 @@
     The confidence interval for the subgroup difference (OR 1.79, 95% CI 1.00 to 3.19) included both a potentially important difference between intervention durations and little or no difference.</t>
       </text>
     </comment>
-    <comment ref="J22" authorId="68" shapeId="0" xr:uid="{E6F372DC-BDEE-4D5F-8590-61CD65813E82}">
+    <comment ref="J22" authorId="72" shapeId="0" xr:uid="{E6F372DC-BDEE-4D5F-8590-61CD65813E82}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -675,7 +714,7 @@
     All included studies were assessed as having moderate risk of bias. High-risk studies were excluded; however, domain-level risk-of-bias assessments were not reported, limiting evaluation of the specific sources and potential impact of bias on the effect estimate.</t>
       </text>
     </comment>
-    <comment ref="J23" authorId="69" shapeId="0" xr:uid="{3337738A-CF20-4907-894A-122DAEC2C52E}">
+    <comment ref="J23" authorId="73" shapeId="0" xr:uid="{3337738A-CF20-4907-894A-122DAEC2C52E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -683,7 +722,7 @@
     All included studies were assessed as having moderate risk of bias. High-risk studies were excluded; however, domain-level risk-of-bias assessments were not reported, limiting evaluation of the specific sources and potential impact of bias on the effect estimate.</t>
       </text>
     </comment>
-    <comment ref="J24" authorId="70" shapeId="0" xr:uid="{AC39B632-C1F6-4A8A-A30D-CF853185D5A1}">
+    <comment ref="J24" authorId="74" shapeId="0" xr:uid="{AC39B632-C1F6-4A8A-A30D-CF853185D5A1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -691,7 +730,7 @@
     All included studies were assessed as having moderate risk of bias. High-risk studies were excluded; however, domain-level risk-of-bias assessments were not reported, limiting evaluation of the specific sources and potential impact of bias on the effect estimate.</t>
       </text>
     </comment>
-    <comment ref="M24" authorId="71" shapeId="0" xr:uid="{0C5C2D5A-4A45-4395-862E-1DB7CDF66554}">
+    <comment ref="M24" authorId="75" shapeId="0" xr:uid="{0C5C2D5A-4A45-4395-862E-1DB7CDF66554}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -699,7 +738,7 @@
     The confidence interval (OR 0.82, 95% CI 0.56 to 1.19) included both a potentially important reduction in suicide attempts and little or no effect.</t>
       </text>
     </comment>
-    <comment ref="J25" authorId="72" shapeId="0" xr:uid="{DE05019E-50FD-4BC2-9816-B945DA689EC3}">
+    <comment ref="J25" authorId="76" shapeId="0" xr:uid="{DE05019E-50FD-4BC2-9816-B945DA689EC3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -707,7 +746,7 @@
     All included studies were assessed as having moderate risk of bias. High-risk studies were excluded; however, domain-level risk-of-bias assessments were not reported, limiting evaluation of the specific sources and potential impact of bias on the effect estimate.</t>
       </text>
     </comment>
-    <comment ref="J26" authorId="73" shapeId="0" xr:uid="{B8C79E6C-9934-46C9-9BAC-944DE549B9B5}">
+    <comment ref="J26" authorId="77" shapeId="0" xr:uid="{B8C79E6C-9934-46C9-9BAC-944DE549B9B5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -715,7 +754,7 @@
     The review included both randomized and non-randomized studies but did not use RoB/ROBINS-I or report risk-of-bias assessments aligned with key GRADE domains. Consequently, important sources of bias, including confounding, selection bias, randomization processes, missing outcome data, and selective reporting, could not be adequately assessed. The authors also reported an overall lack of methodological rigor, including few randomized controlled trials and limited reporting of implementation fidelity and measurement quality.</t>
       </text>
     </comment>
-    <comment ref="K26" authorId="74" shapeId="0" xr:uid="{6D2214B3-8352-4F45-985B-9DAFB8CF4C95}">
+    <comment ref="K26" authorId="78" shapeId="0" xr:uid="{6D2214B3-8352-4F45-985B-9DAFB8CF4C95}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -723,7 +762,7 @@
     Although not reported for this subgroup, only one effect size in the overall forest plot was negative, and that was a college study that would not have been in the high school subgroup </t>
       </text>
     </comment>
-    <comment ref="N26" authorId="75" shapeId="0" xr:uid="{042EC575-5F3E-406D-B267-9CDD6BCA49B9}">
+    <comment ref="N26" authorId="79" shapeId="0" xr:uid="{042EC575-5F3E-406D-B267-9CDD6BCA49B9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -731,7 +770,7 @@
     Although the funnel plot for suicide awareness outcomes showed asymmetry, trim-and-fill analyses did not identify missing studies and provided no evidence that publication bias materially affected the results.</t>
       </text>
     </comment>
-    <comment ref="J27" authorId="76" shapeId="0" xr:uid="{81D41EDA-F79A-4019-B377-B47231E256B4}">
+    <comment ref="J27" authorId="80" shapeId="0" xr:uid="{81D41EDA-F79A-4019-B377-B47231E256B4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -739,7 +778,7 @@
     The review included both randomized and non-randomized studies but did not use RoB/ROBINS-I or report risk-of-bias assessments aligned with key GRADE domains. Consequently, important sources of bias, including confounding, selection bias, randomization processes, missing outcome data, and selective reporting, could not be adequately assessed. The authors also reported an overall lack of methodological rigor, including few randomized controlled trials and limited reporting of implementation fidelity and measurement quality.</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="77" shapeId="0" xr:uid="{033896B8-0274-4184-8625-CACFFF8163FD}">
+    <comment ref="K27" authorId="81" shapeId="0" xr:uid="{033896B8-0274-4184-8625-CACFFF8163FD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -747,7 +786,7 @@
     Although not reported for this subgroup, overall forest plots indicated that effect sizes were on same side of threshold for this outcome.</t>
       </text>
     </comment>
-    <comment ref="N27" authorId="78" shapeId="0" xr:uid="{19192B3E-6221-4F74-A551-29726779B0D9}">
+    <comment ref="N27" authorId="82" shapeId="0" xr:uid="{19192B3E-6221-4F74-A551-29726779B0D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -760,7 +799,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="136">
   <si>
     <t>RefID</t>
   </si>
@@ -834,9 +873,6 @@
     <t>Adolescents in school-based settings versus young adults in college/university settings</t>
   </si>
   <si>
-    <t>OR = 1.19, 95% CI (0.33, 4.35), p = 0.788</t>
-  </si>
-  <si>
     <t>Very serious</t>
   </si>
   <si>
@@ -846,27 +882,15 @@
     <t>Very Low</t>
   </si>
   <si>
-    <t>Universal suicide prevention interventions may not differ in their effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings and with young adults in college/university settings; however, the evidence is very uncertain (OR 1.19, 95% CI 0.33 to 4.35).</t>
-  </si>
-  <si>
     <t>This moderator estimate compares intervention effects between high school and college/university settings and does not provide a stand-alone estimate of intervention effects in high school settings. Key intervention contents included education and/or awareness of suicide risk in young people, but also gatekeeper suicide prevention training of educational staff that involves the identification and referral of the at-risk young people, improved screening of young people for suicide risk by health care professionals, and psychotherapies.</t>
   </si>
   <si>
     <t>Selective prevention</t>
   </si>
   <si>
-    <t>OR = 0.27, 95% CI (0.03, 2.87), p =0.280</t>
-  </si>
-  <si>
-    <t>Selective suicide prevention interventions may have different effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings compared to young adults in college/university settings; however, the evidence is very uncertain (OR 0.27, 95% CI 0.03 to 2.87).</t>
-  </si>
-  <si>
     <t>Indicated prevention</t>
   </si>
   <si>
-    <t>Indicated suicide prevention interventions may have different effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings compared to young adults in college/university settings; however, the evidence is very uncertain (OR 0.27, 95% CI 0.03 to 2.87).</t>
-  </si>
-  <si>
     <t>Suicide Prevention Competencies</t>
   </si>
   <si>
@@ -874,15 +898,6 @@
   </si>
   <si>
     <t>Low</t>
-  </si>
-  <si>
-    <t>Universal suicide prevention interventions may improve suicide prevention competencies (relative to no treatment, waitlist, usual care, or alternative interventions) more with adolescents in school-based settings than young adults in college/university settings (SMD -0.521, 95% CI -0.99 to -0.058).</t>
-  </si>
-  <si>
-    <t>SMD =  -0.069, 95% CI (-0.87, 0.73), p = 0.866</t>
-  </si>
-  <si>
-    <t>Selective suicide prevention interventions may not differ in their effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicide prevention competencies with adolescents in school-based settings and young adults in college/university settings; however, the evidence is very uncertain (SMD −0.07, 95% CI −0.87 to 0.73).</t>
   </si>
   <si>
     <t>Up to 18 years old</t>
@@ -914,9 +929,6 @@
     <t>Moderate</t>
   </si>
   <si>
-    <t>School-based prevention interventions probably reduce suicidal ideation compared with no treatment, usual care, or placebo at 0 to 3 months post-intervention (SMD = 0.15, 95% CI 0.06 to 0.24).</t>
-  </si>
-  <si>
     <t>The review was not restricted to studies that aim to reduce suicidality, but rather included all studies that have included STBs as an outcome measurement to explore potential effects of studies that target risk factors of STBs.</t>
   </si>
   <si>
@@ -926,18 +938,9 @@
     <t>SMD = 0.22, 95% CI (0.05, 0.39)</t>
   </si>
   <si>
-    <t>School-based prevention interventions probably reduce suicidal ideation compared with no treatment, usual care, or placebo at 3 to 12 months follow-up (SMD = 0.22, 95% CI 0.05 to 0.39).</t>
-  </si>
-  <si>
     <t>Targeting STBs as the primary aim of the intervention versus not</t>
   </si>
   <si>
-    <t>SMD = − 0.22 (SE = 0.15), 95% CI (-0.50, 0.07), z = − 1.49, p = 0.136</t>
-  </si>
-  <si>
-    <t>School-based prevention interventions may reduce suicidal ideation (relative to no treatment, usual care, or placebo) at 0 to 3 months post-intervention when they specifically target suicidal thoughts and behaviors (STBs) as their primary aim more than interventions that do not specifically target STBs (SMD difference = -0.22, 95% CI -0.51 to 0.07).</t>
-  </si>
-  <si>
     <t>None (addressed in moderator analysis)</t>
   </si>
   <si>
@@ -947,20 +950,10 @@
     <t>SMD = 0.30, 95% CI (0.15, 0.45)</t>
   </si>
   <si>
-    <t>School-based prevention interventions probably reduce suicidal behaviors compared with no treatment, usual care, or placebo at 0 to 3 months post-intervention (SMD = 0.30, 95% CI 0.15 to 0.45).</t>
-  </si>
-  <si>
     <t>SMD = 0.30, 95% CI (0.16, 0.43)</t>
   </si>
   <si>
     <t>School-based prevention interventions probably reduce suicidal behaviors compared with no treatment, usual care, or placebo at 3 to 12 months follow-up (SMD = 0.30, 95% CI (0.16, 0.43).</t>
-  </si>
-  <si>
-    <t>Contrast SMD = − 0.87 (SE = 0.28), 95% CI (-1.42, -0.31), z = -3.04, p = 0.002
-- Within-group interventions targeting STBs: SMD = 0.23, p &lt; 0.001</t>
-  </si>
-  <si>
-    <t>School-based prevention interventions probably reduce suicidal behaviors (relative to no treatment, usual care, or placebo) at 0 to 3 months post-intervention when they specifically target suicidal thoughts and behaviors (STBs) as their primary aim less than interventions that do not specifically target STBs (SMD difference = -0.87, 95% CI -1.42 to -0.31; within-group primarily targets STBs intervention effect: SMD = 0.23, p &lt; 0.001).</t>
   </si>
   <si>
     <t>Adolescents aged 11–19 years attending post-primary school</t>
@@ -977,9 +970,6 @@
     <t>OR = 0.85, 95% CI (0.75, 0.95)</t>
   </si>
   <si>
-    <t>School-based suicide prevention interventions probably reduce suicidal ideation compared with no intervention, waitlist, or alternative interventions (OR 0.85, 95% CI 0.75 to 0.95).</t>
-  </si>
-  <si>
     <t>The review was not restricted to studies that aim to reduce suicidality, including interventions that do not directly target STBs.</t>
   </si>
   <si>
@@ -989,89 +979,27 @@
     <t>OR = 0.72, 95% CI (0.59, 0.87)</t>
   </si>
   <si>
-    <t>School-based suicide prevention interventions probably reduce suicide attempts compared with no intervention, waitlist, or alternative interventions (OR 0.72, 95% CI 0.59 to 0.87).</t>
-  </si>
-  <si>
     <t>Teacher/counselor involvement versus no school stakeholder involvement</t>
   </si>
   <si>
-    <t>Contrast OR = 1.57, 95% CI (0.93, 2.61).
-No school stakeholder involvement: within group OR = 0.68 (no CI), p&lt;0.001.
-Teacher or counsellor involvement: within group OR = 1.06 (no CI).</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions without school stakeholder involvement may reduce suicide attempts more than interventions involving teachers or counsellors (OR for subgroup contrast = 1.57, 95% CI 0.93 to 2.61; within-group ORs = 0.68 [p &lt; 0.001] and 1.06, respectively).</t>
-  </si>
-  <si>
-    <t>The review was not restricted to studies that aim to reduce suicidality, including interviews that do not directly target STBs.</t>
-  </si>
-  <si>
     <t>Multi-stakeholder involvement versus no school stakeholder involvement</t>
   </si>
   <si>
-    <t>Contrast OR = 0.92, 95% CI (0.59, 1.45).
-No school stakeholder involvement: within group OR = 0.68 (no CI).
-Mutli-stakeholder involvement: within group OR = 0.63 (no CI), p&lt;0.01.</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may not differ in their effects on suicide attempts based on whether they involve multiple stakeholders or not (OR for subgroup contrast = 0.92, 95% CI 0.59 to 1.45; within-group ORs  = 0.63 [p &lt; 0.01] and 0.68, respectively).</t>
-  </si>
-  <si>
-    <t>Contrast OR = 0.60, 95% CI (0.35, 1.02).
-No (not primarily targeting STBs) within group OR = 1.11 (no CI).
-Yes (primarily targeting STBs) within group OR = 0.67 (no CI), p&lt;0.001.</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions that primarily target suicidal thoughts and behaviors (STBs) may reduce suicide attempts more than interventions that do not primarily target STBs (subgroup-contrast OR = 0.60, 95% CI 0.35 to 1.02; within-group ORs = 0.67 [p &lt; 0.001]  and 1.11, respectively).</t>
-  </si>
-  <si>
     <t>Follow-up (12 months)</t>
   </si>
   <si>
     <t>12-months follow-up versus  ≤ 3-months follow-up</t>
   </si>
   <si>
-    <t>Contrast OR = 0.85, 95% CI (0.55, 1.30).
-≤ 3-months follow-up: within group OR = 0.70 (no CI),  p&lt;0.01.
-12-months follow-up: within group OR = 0.59 (no CI), p&lt;0.01.</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may not differ in their effects on suicide attempts at 12-month follow-up compared with follow-up periods shorter than 3 months (OR for subgroup contrast = 0.85, 95% CI 0.55 to 1.30; within-group ORs = 0.59 [p &lt; 0.01] and 0.70 [p &lt; 0.01], respectively).</t>
-  </si>
-  <si>
     <t>17-20-months follow-up versus  ≤ 3-months follow-up</t>
   </si>
   <si>
-    <t>Contrast OR = 1.52, 95% CI (0.90, 2.59).
-≤ 3-months follow-up: within group OR = 0.70 (no CI),  p&lt;0.01.
-17-20-months follow-up: within group OR = 1.06 (no CI).</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts less at 17-20-month follow-up than at follow-up periods of 3 months or less (OR for subgroup contrast = 1.52, 95% CI 0.90 to 2.59; within-group ORs = 1.06 and 0.70, respectively).</t>
-  </si>
-  <si>
     <t>4-weeks intervention duration versus ≤ 1-week intervention duration</t>
   </si>
   <si>
-    <t>Contrast OR = 1.13, 95% CI (0.76, 1.68).
-≤ 1-week intervention duration: within group OR = 0.62 (no CI),  p&lt;0.01.
-4-weeks intervention duration: within group OR = 0.70 (no CI),  p&lt;0.01.</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may not differ in their effects on suicide attempts based on whether intervention duration is 4 weeks versus 1 week or less (OR for subgroup contrast = 1.13, 95% CI 0.76 to 1.68; within-group ORs = 0.70 [p &lt; 0.01] and 0.62 [p &lt; 0.01], respectively).</t>
-  </si>
-  <si>
     <t>4-104 weeks intervention duration versus ≤ 1-week intervention duration</t>
   </si>
   <si>
-    <t>Contrast OR = 1.79, 95% CI (1.00, 3.19).
-≤ 1-week intervention duration: within group OR = 0.62 (no CI),  p&lt;0.01.
-4-104 weeks duration: within group OR = 1.11 (no CI).</t>
-  </si>
-  <si>
-    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts less when intervention duration is 4 to 104 weeks than when intervention duration is 1 week or less (OR for subgroup contrast = 1.79, 95% CI 1.00 to 3.19; within-group ORs = 1.11 and 0.62 [p &lt; 0.01], respectively).</t>
-  </si>
-  <si>
     <t>Pupils (assumed K-12)</t>
   </si>
   <si>
@@ -1084,33 +1012,9 @@
     <t>3-month follow-up</t>
   </si>
   <si>
-    <t>OR = 0.56, 95% CI (0.39, 0.80), z = 3.20, p = 0.001</t>
-  </si>
-  <si>
-    <t>School-based education interventions probably reduce suicide attempts (relative to unclear comparator interventions) at 3-month follow-up (OR 0.56, 95% CI 0.39 to 0.80).</t>
-  </si>
-  <si>
     <t>12-month follow-up</t>
   </si>
   <si>
-    <t>OR = 0.60, 95% CI (0.38, 0.95), z = 2.16, p = 0.03</t>
-  </si>
-  <si>
-    <t>School-based education interventions probably reduce suicide attempts (relative to unclear comparator interventions) at 12-month follow-up (OR 0.60, 95% CI 0.38 to 0.95).</t>
-  </si>
-  <si>
-    <t>OR = 0.82, 95% CI (0.56, 1.19), z = 1.07, p = 0.29</t>
-  </si>
-  <si>
-    <t>School-based education interventions may reduce suicidal ideation (relative to unclear comparator interventions) at 3-month follow-up (OR 0.82, 95% CI 0.56 to 1.19).</t>
-  </si>
-  <si>
-    <t>OR = 0.54, 95% CI (0.35, 0.81), z = 2.96, p = 0.003</t>
-  </si>
-  <si>
-    <t>School-based education interventions probably reduce suicidal ideation (relative to unclear comparator interventions) at 12-month follow-up (OR 0.54, 95% CI 0.35 to 0.81).</t>
-  </si>
-  <si>
     <t>School-based suicide prevention interventions</t>
   </si>
   <si>
@@ -1129,30 +1033,14 @@
     <t>SMD = 0.63, 95% CI (0.42, 0.84)</t>
   </si>
   <si>
-    <t>School-based suicide prevention interventions may increase suicide awareness (relative to any comparator intervention) among high school students (g = 0.63, 95% CI 0.42 to 0.84).</t>
-  </si>
-  <si>
     <t>Helping Skills</t>
   </si>
   <si>
     <t>SMD = 0.38, 95% CI (0.28, 0.50)</t>
-  </si>
-  <si>
-    <t>School-based suicide prevention interventions may improve helping skills (relative to any comparator intervention) among high school students (g = 0.38, 95% CI 0.28 to 0.50).</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">This moderator estimate compares intervention effects between high school and college/university settings and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>does not provide a stand-alone estimate of intervention effects in high school settings</t>
     </r>
     <r>
       <rPr>
@@ -1162,8 +1050,220 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Key intervention contents included education and/or awareness of suicide risk in young people, but also gatekeeper suicide prevention training of educational staff that involves the identification and referral of the at-risk young people, improved screening of young people for suicide risk by health care professionals, and psychotherapies.</t>
+      <t>does not provide a stand-alone estimate of intervention effects in high school settings. Key intervention contents included education and/or awareness of suicide risk in young people, but also gatekeeper suicide prevention training of educational staff that involves the identification and referral of the at-risk young people, improved screening of young people for suicide risk by health care professionals, and psychotherapies.</t>
     </r>
+  </si>
+  <si>
+    <t>OR = 1.19, 95% CI (0.33, 4.35), p = .788</t>
+  </si>
+  <si>
+    <t>OR = 0.27, 95% CI (0.03, 2.87), p = .280</t>
+  </si>
+  <si>
+    <t>Contrast OR = 1.57, 95% CI (0.93, 2.61).
+No school stakeholder involvement: within group OR = 0.68 (no CI), p &lt; .001.
+Teacher or counsellor involvement: within group OR = 1.06 (no CI).</t>
+  </si>
+  <si>
+    <t>Contrast OR = 0.92, 95% CI (0.59, 1.45).
+No school stakeholder involvement: within group OR = 0.68 (no CI).
+Mutli-stakeholder involvement: within group OR = 0.63 (no CI), p &lt; .01.</t>
+  </si>
+  <si>
+    <t>Contrast OR = 0.60, 95% CI (0.35, 1.02).
+No (not primarily targeting STBs) within group OR = 1.11 (no CI).
+Yes (primarily targeting STBs) within group OR = 0.67 (no CI), p &lt; .001.</t>
+  </si>
+  <si>
+    <t>Contrast OR = 0.85, 95% CI (0.55, 1.30).
+≤ 3-months follow-up: within group OR = 0.70 (no CI),  p &lt; .01.
+12-months follow-up: within group OR = 0.59 (no CI), p &lt; .01.</t>
+  </si>
+  <si>
+    <t>Contrast OR = 1.52, 95% CI (0.90, 2.59).
+≤ 3-months follow-up: within group OR = 0.70 (no CI),  p &lt; .01.
+17-20-months follow-up: within group OR = 1.06 (no CI).</t>
+  </si>
+  <si>
+    <t>Contrast OR = 1.13, 95% CI (0.76, 1.68).
+≤ 1-week intervention duration: within group OR = 0.62 (no CI),  p &lt; .01.
+4-weeks intervention duration: within group OR = 0.70 (no CI),  p &lt; .01.</t>
+  </si>
+  <si>
+    <t>Contrast OR = 1.79, 95% CI (1.00, 3.19).
+≤ 1-week intervention duration: within group OR = 0.62 (no CI),  p &lt; .01.
+4-104 weeks duration: within group OR = 1.11 (no CI).</t>
+  </si>
+  <si>
+    <t>OR = 0.56, 95% CI (0.39, 0.80), z = 3.20, p = .001</t>
+  </si>
+  <si>
+    <t>OR = 0.60, 95% CI (0.38, 0.95), z = 2.16, p = .03</t>
+  </si>
+  <si>
+    <t>OR = 0.82, 95% CI (0.56, 1.19), z = 1.07, p = .29</t>
+  </si>
+  <si>
+    <t>OR = 0.54, 95% CI (0.35, 0.81), z = 2.96, p = .003</t>
+  </si>
+  <si>
+    <t>SMD = -0.069, 95% CI (-0.87, 0.73), p = .866</t>
+  </si>
+  <si>
+    <t>School-based suicide prevention interventions probably reduce suicidal ideation compared with no intervention, waitlist, or alternative interventions (OR 0.85, 95% CI 0.75, 0.95).</t>
+  </si>
+  <si>
+    <t>School-based suicide prevention interventions probably reduce suicide attempts compared with no intervention, waitlist, or alternative interventions (OR 0.72, 95% CI 0.59, 0.87).</t>
+  </si>
+  <si>
+    <t>School-based prevention interventions probably reduce suicidal ideation compared with no treatment, usual care, or placebo at 0 to 3 months post-intervention (SMD = 0.15, 95% CI 0.06, 0.24).</t>
+  </si>
+  <si>
+    <t>School-based prevention interventions probably reduce suicidal ideation compared with no treatment, usual care, or placebo at 3 to 12 months follow-up (SMD = 0.22, 95% CI 0.05, 0.39).</t>
+  </si>
+  <si>
+    <t>School-based prevention interventions probably reduce suicidal behaviors compared with no treatment, usual care, or placebo at 0 to 3 months post-intervention (SMD = 0.30, 95% CI 0.15, 0.45).</t>
+  </si>
+  <si>
+    <t>School-based prevention interventions probably reduce suicidal behaviors (relative, no treatment, usual care, or placebo) at 0 to 3 months post-intervention when they specifically target suicidal thoughts and behaviors (STBs) as their primary aim less than interventions that do not specifically target STBs (SMD difference = -0.87, 95% CI -1.42, -0.31; within-group primarily targets STBs intervention effect: SMD = 0.23, p &lt; 0.001).</t>
+  </si>
+  <si>
+    <t>School-based prevention interventions may reduce suicidal ideation (relative, no treatment, usual care, or placebo) at 0 to 3 months post-intervention when they specifically target suicidal thoughts and behaviors (STBs) as their primary aim less than interventions that do not specifically target STBs (SMD difference = -0.22, 95% CI -0.50, 0.07).</t>
+  </si>
+  <si>
+    <t>Contrast SMD = -0.87 (SE = 0.28), 95% CI (-1.42, -0.31), z = -3.04, p = .002
+- Within-group interventions targeting STBs: SMD = 0.23, p &lt; .001</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions without school stakeholder involvement may reduce suicide attempts more than interventions involving teachers or counsellors (OR for subgroup contrast = 1.57, 95% CI 0.93, 2.61; within-group ORs = 0.68 [p &lt; 0.001] and 1.06, respectively).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may not differ in their effects on suicide attempts based on whether they involve multiple stakeholders or not (OR for subgroup contrast = 0.92, 95% CI 0.59, 1.45; within-group ORs  = 0.63 [p &lt; 0.01] and 0.68, respectively).</t>
+  </si>
+  <si>
+    <t>Universal suicide prevention interventions may improve suicide prevention competencies (relative to no treatment, waitlist, usual care, or alternative interventions) more with adolescents in school-based settings than young adults in college/university settings (SMD -0.52, 95% CI -0.99, -0.06).</t>
+  </si>
+  <si>
+    <t>Selective suicide prevention interventions may have different effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings compared, young adults in college/university settings; however, the evidence is very uncertain (OR 0.27, 95% CI 0.03, 2.87).</t>
+  </si>
+  <si>
+    <t>Universal suicide prevention interventions may differ in their effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings and with young adults in college/university settings; however, the evidence is very uncertain (OR 1.19, 95% CI 0.33, 4.35).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions that primarily target suicidal thoughts and behaviors (STBs) may reduce suicide attempts more than interventions that do not primarily target STBs (subgroup-contrast OR = 0.60, 95% CI 0.35, 1.02; within-group ORs = 0.67 [p &lt; 0.001]  and 1.11, respectively).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts less at 17-20-month follow-up than at follow-up periods of 3 months or less (OR for subgroup contrast = 1.52, 95% CI 0.90, 2.59; within-group ORs = 1.06 and 0.70, respectively).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts less when intervention duration is 4-104 weeks than when intervention duration is 1 week or less (OR for subgroup contrast = 1.79, 95% CI 1.00, 3.19; within-group ORs = 1.11 and 0.62 [p &lt; 0.01], respectively).</t>
+  </si>
+  <si>
+    <t>School-based education interventions probably reduce suicide attempts (relative to unclear comparator interventions) at 3-month follow-up (OR 0.56, 95% CI 0.39, 0.80).</t>
+  </si>
+  <si>
+    <t>School-based education interventions probably reduce suicide attempts (relative to unclear comparator interventions) at 12-month follow-up (OR 0.60, 95% CI 0.38, 0.95).</t>
+  </si>
+  <si>
+    <t>School-based education interventions may reduce suicidal ideation (relative to unclear comparator interventions) at 3-month follow-up (OR 0.82, 95% CI 0.56, 1.19).</t>
+  </si>
+  <si>
+    <t>School-based education interventions probably reduce suicidal ideation (relative to unclear comparator interventions) at 12-month follow-up (OR 0.54, 95% CI 0.35, 0.81).</t>
+  </si>
+  <si>
+    <t>School-based suicide prevention interventions may improve helping skills (relative to any comparator intervention) among high school students (g = 0.38, 95% CI 0.28, 0.50).</t>
+  </si>
+  <si>
+    <t>School-based suicide prevention interventions may increase suicide awareness (relative to any comparator intervention) among high school students (g = 0.63, 95% CI 0.42, 0.84).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts more at 12-month follow-up than at follow-up periods of 3 months or less (OR for subgroup contrast = 0.85, 95% CI 0.55, 1.30; within-group ORs = 0.59 [p &lt; 0.01] and 0.70 [p &lt; 0.01], respectively).</t>
+  </si>
+  <si>
+    <t>Selective suicide prevention interventions may have different effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicide prevention comptencies with adolescents in school-based settings compared to young adults in college/university settings; however, the evidence is very uncertain (SMD -0.07, 95% CI -0.87, 0.73).</t>
+  </si>
+  <si>
+    <t>Indicated suicide prevention interventions may have different effects (relative to no treatment, waitlist, usual care, or alternative interventions) on suicidality with adolescents in school-based settings compared to young adults in college/university settings; however, the evidence is very uncertain (OR 0.27, 95% CI 0.03, 2.87).</t>
+  </si>
+  <si>
+    <t>Relative to comparator interventions (no treatment, waitlist, or alternative interventions), school-based suicide prevention interventions may reduce suicide attempts less when intervention duration is 4 weeks than when intervention duration is 1 week or less (OR for subgroup contrast = 1.13, 95% CI 0.76, 1.68; within-group ORs = 0.70 [p &lt; 0.01] and 0.62 [p &lt; 0.01], respectively).</t>
+  </si>
+  <si>
+    <t>Data Collection Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The forest plot for this estimate (Figure S4) contains a 95% confidence interval for one study (Fekkes et al, 2016) with an unlikely range of 0 to 3877.73. This interval does not match the confidence interval reported in the original study manuscript and may reflect a recalculation or error. The study is weighted 0.05% in the meta-analysis so did not have a large impact on the overall estimate. We attempted to contact the corresponding author via email to clarify. </t>
+  </si>
+  <si>
+    <t>This estimate came from the review text on page 414 of the report pdf. It appears to differ from the estimate in the corresponding forest plot (Figure 7) of SMD = 0.29, 95% CI [0.14, 0.44]. We attempted to contact the corresponding author via email.</t>
+  </si>
+  <si>
+    <t>All contrast odds ratios for this review have been transformed from author-reported log odds coefficients for interpretability.</t>
+  </si>
+  <si>
+    <t>All contrast odds ratios for this review have been transformed from author-reported log odds coefficients for interpretability. Estimates for indicated and selective interventions on suicidality outcomes were identical for the school vs. university/college contrasts in Supplemental Material 9 and we are not sure if they may reflect an error. We were unable to reach the corresponding author via the provided email address provided in the manuscript.</t>
+  </si>
+  <si>
+    <t>We transformed author-reported contrast log odds ratios to odds ratios for this review for interpretability.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The upper limit of the confidence interval was corrected by our team from −0.07 (as reported in the original review) to 0.07 based on the corresponding </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">value. </t>
+    </r>
+  </si>
+  <si>
+    <t>Favored group</t>
+  </si>
+  <si>
+    <t>Cannot detect due to Very Low certainty rating</t>
+  </si>
+  <si>
+    <t>Adolescents in school-based settings</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Targeting STBs as the primary aim of the intervention</t>
+  </si>
+  <si>
+    <t>No stakeholder involvement</t>
+  </si>
+  <si>
+    <t>No difference</t>
+  </si>
+  <si>
+    <t>Not specifically targeting STBs as the primary aim of the intervention</t>
+  </si>
+  <si>
+    <t>≤ 1-week intervention duration</t>
+  </si>
+  <si>
+    <t>≤ 3-months follow-up</t>
+  </si>
+  <si>
+    <t>Contrast SMD = -0.22 (SE = 0.15), 95% CI (-0.50, 0.07), z = -1.49, p = .136</t>
   </si>
 </sst>
 </file>
@@ -1187,19 +1287,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1214,7 +1327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1223,6 +1336,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1578,6 +1703,9 @@
   <threadedComment ref="M2" dT="2026-08-10T21:33:09.96" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{8934C9EC-E1EE-46D6-8DA8-2B9FF162A1D0}">
     <text>Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</text>
   </threadedComment>
+  <threadedComment ref="P2" dT="2026-09-09T20:00:53.52" personId="{A3118CA8-423B-45AA-8B36-055340945409}" id="{BED55A21-DC3F-4007-9678-FB4C496D0766}">
+    <text>Changed from “may not” to “may” due to OR = 1.19</text>
+  </threadedComment>
   <threadedComment ref="I3" dT="2026-08-14T16:28:43.29" personId="{A3118CA8-423B-45AA-8B36-055340945409}" id="{F97111A4-3E40-475D-BCDC-D4AE2090472B}">
     <text>Odds ratios are transformed from log odds. Note this estimate is identical to the one below and may reflect an error.</text>
   </threadedComment>
@@ -1616,6 +1744,9 @@
   </threadedComment>
   <threadedComment ref="M6" dT="2026-08-10T21:33:09.96" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{6A8CDA2D-B191-45D2-8FA0-3B85CBC64D5A}">
     <text>Downgraded two levels due to very serious imprecision; the 95% CI around the effect estimate was wide and included substantial benefit, no effect, and substantial harm.</text>
+  </threadedComment>
+  <threadedComment ref="P6" dT="2026-09-09T20:01:42.19" personId="{A3118CA8-423B-45AA-8B36-055340945409}" id="{86961469-68F5-4DE4-B96E-A21549C91143}">
+    <text>Changed from “may not” to “may” due to SMD = -0.07, which is just outside -0.05 threshold.</text>
   </threadedComment>
   <threadedComment ref="J7" dT="2026-08-11T01:19:49.49" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{B3B7AC91-FBC3-436C-82DE-F9246BC66C0F}">
     <text>Although most studies were judged at low risk across assessed domains and no concerns regarding selective reporting were identified, blinding was not assessed because it was considered infeasible for psychological interventions, outcomes were primarily self-reported, and most studies did not use intention-to-treat analyses.</text>
@@ -1744,6 +1875,9 @@
   <threadedComment ref="M18" dT="2026-08-12T00:58:27.88" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{5DD21839-2B0C-418E-B342-E81FEC740430}">
     <text>The confidence interval for the subgroup difference (OR 0.85, 95% CI 0.55 to 1.30) included both potentially important differences between follow-up periods and little or no difference.</text>
   </threadedComment>
+  <threadedComment ref="P18" dT="2026-09-09T20:04:07.70" personId="{A3118CA8-423B-45AA-8B36-055340945409}" id="{25CA98DB-9416-4171-B283-93B8471A8D4C}">
+    <text>Changed from “may not” to “may” due to contrast OR = 0.85, which is below lower threshold bound of 0.91. Also added effect direction of more for 12-months due to OR &lt;1 relative to reference group.</text>
+  </threadedComment>
   <threadedComment ref="J19" dT="2026-08-11T17:41:25.23" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{B375F206-DA05-4342-8601-843499F31D95}">
     <text>Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</text>
   </threadedComment>
@@ -1761,6 +1895,9 @@
   </threadedComment>
   <threadedComment ref="M20" dT="2026-08-12T01:12:46.64" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{99297B65-3A3E-4912-A925-C2EE27D33BA1}">
     <text>The confidence interval for the subgroup difference (OR 1.13, 95% CI 0.76 to 1.68) included both potentially important differences between intervention durations and little or no difference.</text>
+  </threadedComment>
+  <threadedComment ref="P20" dT="2026-09-09T20:05:03.51" personId="{A3118CA8-423B-45AA-8B36-055340945409}" id="{8C0BDE33-B1B8-4444-945F-536D8A6CE891}">
+    <text>Changed from “may not” to “may” due to contrast OR 1.13, which is above upper threshold of 1.10. Also added direction of difference.</text>
   </threadedComment>
   <threadedComment ref="J21" dT="2026-08-11T17:41:25.23" personId="{3820DA5F-3A24-4A0A-869D-42B866745168}" id="{7D1AEF54-A107-4CB5-82AC-2827C98B97E0}">
     <text>Although half of the included studies were assessed as low risk of bias, the review omitted assessment of some bias domains, including bias in outcome measurement, only a subset of studies underwent duplicate risk-of-bias assessment, and one-third of included studies were rated at high risk of bias.</text>
@@ -1809,7 +1946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908A1C94-6D85-4A17-8A3E-62261EF39AA4}">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1827,12 +1964,13 @@
     <col min="13" max="13" width="27.28515625" style="2" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.28515625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="69.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="68.7109375" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="2"/>
+    <col min="16" max="16" width="69.28515625" style="6" customWidth="1"/>
+    <col min="17" max="18" width="68.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="47.85546875" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1878,14 +2016,20 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>6</v>
       </c>
@@ -1910,35 +2054,41 @@
       <c r="H2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>28</v>
+      <c r="R2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>6</v>
       </c>
@@ -1949,7 +2099,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
@@ -1963,35 +2113,41 @@
       <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>30</v>
+      <c r="I3" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>28</v>
+      <c r="R3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>6</v>
       </c>
@@ -2002,7 +2158,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>19</v>
@@ -2016,35 +2172,41 @@
       <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
+      <c r="I4" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>28</v>
+      <c r="R4" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>6</v>
       </c>
@@ -2061,7 +2223,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -2069,35 +2231,38 @@
       <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
+      <c r="I5" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>119</v>
+        <v>77</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -2108,13 +2273,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
@@ -2122,35 +2287,38 @@
       <c r="H6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>38</v>
+      <c r="I6" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>28</v>
+      <c r="R6" s="4" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>11</v>
       </c>
@@ -2158,52 +2326,55 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="P7" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>50</v>
+      <c r="R7" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>11</v>
       </c>
@@ -2211,52 +2382,55 @@
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="P8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>50</v>
+      <c r="R8" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>11</v>
       </c>
@@ -2264,52 +2438,58 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="S9" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>11</v>
       </c>
@@ -2317,52 +2497,55 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="P10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>50</v>
+      <c r="R10" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -2370,52 +2553,58 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="P11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>50</v>
+      <c r="R11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2423,52 +2612,55 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>64</v>
+      <c r="P12" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2476,52 +2668,55 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2529,52 +2724,58 @@
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>73</v>
+        <v>40</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2582,52 +2783,58 @@
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -2635,52 +2842,58 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -2688,52 +2901,55 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>82</v>
+        <v>31</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -2741,52 +2957,58 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>86</v>
+        <v>31</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>12</v>
       </c>
@@ -2794,52 +3016,58 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>89</v>
+        <v>31</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>12</v>
       </c>
@@ -2847,52 +3075,58 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>92</v>
+        <v>31</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>12</v>
       </c>
@@ -2900,52 +3134,58 @@
         <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>95</v>
+        <v>31</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2953,52 +3193,55 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3006,52 +3249,55 @@
         <v>2</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>104</v>
+        <v>40</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -3059,52 +3305,55 @@
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>106</v>
+        <v>31</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>20</v>
       </c>
@@ -3112,52 +3361,55 @@
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>108</v>
+        <v>40</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>3485</v>
       </c>
@@ -3168,49 +3420,52 @@
         <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="Q26" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>3485</v>
       </c>
@@ -3221,50 +3476,54 @@
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="Q27" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:Q27">
+  <autoFilter ref="A1:Q27" xr:uid="{908A1C94-6D85-4A17-8A3E-62261EF39AA4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q27">
     <sortCondition ref="A2:A27"/>
     <sortCondition ref="B2:B27"/>
   </sortState>
@@ -3535,15 +3794,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="05f91a1b-dc9e-4935-83bb-8b16b289603f">
@@ -3552,6 +3802,15 @@
     <TaxCatchAll xmlns="031df1fd-70ca-41ea-9254-2ad0543794df" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3574,14 +3833,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED58472-CE18-49FC-87DA-D48D3D806B62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F79E4227-E673-45FF-940E-BE98267F825D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3590,4 +3841,12 @@
     <ds:schemaRef ds:uri="031df1fd-70ca-41ea-9254-2ad0543794df"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED58472-CE18-49FC-87DA-D48D3D806B62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>